--- a/storage/templates/loan_billing_template.xlsx
+++ b/storage/templates/loan_billing_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lerry/Herd/sksumpc/storage/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72C2EE6-C9FB-5B4E-884F-802DAC1CDAAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{081C9C6B-8997-7C49-9E7A-2DF28BEADB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -178,20 +178,20 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -482,24 +482,24 @@
     <col min="3" max="3" width="23.5" style="17" customWidth="1"/>
     <col min="4" max="4" width="45.83203125" customWidth="1"/>
     <col min="5" max="5" width="23.5" customWidth="1"/>
-    <col min="6" max="6" width="41" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.5" style="12" customWidth="1"/>
-    <col min="8" max="8" width="27.5" style="22" customWidth="1"/>
-    <col min="9" max="9" width="26.5" style="22" customWidth="1"/>
+    <col min="8" max="8" width="19.1640625" style="21" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -534,10 +534,10 @@
       <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="18" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="2"/>
@@ -560,8 +560,8 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -582,8 +582,8 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -604,8 +604,8 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -618,8 +618,8 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
